--- a/题库/PY选择题练习.xlsx
+++ b/题库/PY选择题练习.xlsx
@@ -378,7 +378,7 @@
     <t>&gt;&gt;&gt; 'ABCD' == 'abcd'.upper()</t>
   </si>
   <si>
-    <t>&gt;&gt;&gt; 'c' &lt; 'a'</t>
+    <t>&gt;&gt;&gt; '' &lt; 'a'</t>
   </si>
   <si>
     <t>&gt;&gt;&gt; 'python' &lt; 'pypi'</t>
@@ -898,6 +898,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>下列程序的输出结果是</t>
     </r>
     <r>
@@ -950,7 +956,27 @@
     <t>数组</t>
   </si>
   <si>
-    <t>关于Python程序格式框架的描述，以下选项中错误的是 (A)Python语言不采用严格的“缩进”来表明程序的格式框架 (B)Python语言的缩进可以采用Tab键实现 (C)Python单层缩进代码属于之前最邻近的一行非缩进代码，多层缩进代码根据缩进关系决定所属范围 (D)判断、循环、函数等语法形式能够通过缩进包含一批Python代码，进而表达对应的语义</t>
+    <r>
+      <t>关于</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Python</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>程序格式框架的描述，以下选项中错误的是</t>
+    </r>
   </si>
   <si>
     <t>Python语言不采用严格的“缩进”来表明程序的格式框架</t>
@@ -1253,7 +1279,56 @@
     <t>jieba.add_word(s)是向分词词典里增加新词</t>
   </si>
   <si>
-    <t>t=(1,2,3) a,b,c=t 则a等于()。</t>
+    <r>
+      <t xml:space="preserve">t=(1,2,3)
+a,b,c=t 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>则</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>等于</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
   </si>
   <si>
     <t>下列程序的输出结果是()。f=open('c:\out.txt','w+') f.write('Python') f.seek(0) c=f.read(2) print(c) f.close()</t>
@@ -1593,6 +1668,12 @@
       <sz val="11.5"/>
       <color rgb="FF0F1115"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11.5"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1738,12 +1819,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11.5"/>
-      <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
-      <charset val="134"/>
     </font>
     <font>
       <i/>
@@ -2120,137 +2195,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2276,6 +2351,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4364,14 +4442,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" ht="409.5" spans="1:9">
+    <row r="62" ht="162" spans="1:9">
       <c r="A62" s="4">
         <v>61</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="C62" s="6" t="s">
         <v>256</v>
       </c>
       <c r="D62" s="4" t="s">
@@ -4864,7 +4942,7 @@
       <c r="B79" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C79" s="4" t="s">
+      <c r="C79" s="9" t="s">
         <v>336</v>
       </c>
       <c r="D79" s="4">
